--- a/panchang-data/Kolkata2026.xlsx
+++ b/panchang-data/Kolkata2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5398">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16219,6 +16219,9 @@
   </si>
   <si>
     <t>121°05'10.74</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16708,7 +16711,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16794,7 +16797,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>50</v>
@@ -16880,7 +16883,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -16966,7 +16969,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>89</v>
@@ -17052,7 +17055,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>108</v>
@@ -17138,7 +17141,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>125</v>
@@ -17224,7 +17227,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>143</v>
@@ -17310,7 +17313,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17396,7 +17399,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>50</v>
@@ -17482,7 +17485,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17568,7 +17571,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>89</v>
@@ -17654,7 +17657,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>108</v>
@@ -17740,7 +17743,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>125</v>
@@ -17826,7 +17829,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>143</v>
@@ -17912,7 +17915,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -17998,7 +18001,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>50</v>
@@ -18084,7 +18087,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18170,7 +18173,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>89</v>
@@ -18256,7 +18259,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>108</v>
@@ -18342,7 +18345,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>125</v>
@@ -18428,7 +18431,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>143</v>
@@ -18514,7 +18517,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18600,7 +18603,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>50</v>
@@ -18686,7 +18689,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18772,7 +18775,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>89</v>
@@ -18858,7 +18861,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>108</v>
@@ -18944,7 +18947,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>125</v>
@@ -19030,7 +19033,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>143</v>
@@ -19116,7 +19119,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19202,7 +19205,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>50</v>
@@ -19288,7 +19291,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19374,7 +19377,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>88</v>
+        <v>565</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>89</v>
@@ -19460,7 +19463,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>108</v>
@@ -19546,7 +19549,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>125</v>
@@ -19632,7 +19635,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>143</v>
@@ -19718,7 +19721,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19804,7 +19807,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>50</v>
@@ -19890,7 +19893,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -19976,7 +19979,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>89</v>
@@ -20062,7 +20065,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>108</v>
@@ -20148,7 +20151,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>125</v>
@@ -20234,7 +20237,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>143</v>
@@ -20320,7 +20323,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20406,7 +20409,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>50</v>
@@ -20492,7 +20495,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20578,7 +20581,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>89</v>
@@ -20664,7 +20667,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>108</v>
@@ -20750,7 +20753,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>125</v>
@@ -20836,7 +20839,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>143</v>
@@ -20922,7 +20925,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -21008,7 +21011,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>50</v>
@@ -21094,7 +21097,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21180,7 +21183,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>89</v>
@@ -21266,7 +21269,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>108</v>
@@ -21352,7 +21355,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>125</v>
@@ -21438,7 +21441,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>143</v>
@@ -21524,7 +21527,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21610,7 +21613,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>50</v>
@@ -21696,7 +21699,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21782,7 +21785,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>89</v>
@@ -21868,7 +21871,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>108</v>
@@ -21954,7 +21957,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>565</v>
+        <v>1006</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>125</v>
@@ -22040,7 +22043,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>143</v>
@@ -22126,7 +22129,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22212,7 +22215,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>50</v>
@@ -22298,7 +22301,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22384,7 +22387,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>89</v>
@@ -22470,7 +22473,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>108</v>
@@ -22556,7 +22559,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>125</v>
@@ -22642,7 +22645,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>143</v>
@@ -22728,7 +22731,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22814,7 +22817,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>50</v>
@@ -22900,7 +22903,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -22986,7 +22989,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>89</v>
@@ -23072,7 +23075,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>108</v>
@@ -23158,7 +23161,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>125</v>
@@ -23244,7 +23247,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>143</v>
@@ -23330,7 +23333,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23416,7 +23419,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>50</v>
@@ -23502,7 +23505,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23588,7 +23591,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>89</v>
@@ -23674,7 +23677,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>108</v>
@@ -23760,7 +23763,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>125</v>
@@ -23846,7 +23849,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>143</v>
@@ -23932,7 +23935,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -24018,7 +24021,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>50</v>
@@ -24104,7 +24107,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24190,7 +24193,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>89</v>
@@ -24276,7 +24279,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>108</v>
@@ -24362,7 +24365,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>125</v>
@@ -24448,7 +24451,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>143</v>
@@ -24534,7 +24537,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1006</v>
+        <v>1446</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24620,7 +24623,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>50</v>
@@ -24706,7 +24709,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24792,7 +24795,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>89</v>
@@ -24878,7 +24881,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>108</v>
@@ -24964,7 +24967,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>125</v>
@@ -25050,7 +25053,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>143</v>
@@ -25136,7 +25139,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25222,7 +25225,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>50</v>
@@ -25308,7 +25311,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25394,7 +25397,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>89</v>
@@ -25480,7 +25483,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>108</v>
@@ -25566,7 +25569,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>125</v>
@@ -25652,7 +25655,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>143</v>
@@ -25738,7 +25741,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25824,7 +25827,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>50</v>
@@ -25910,7 +25913,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -25996,7 +25999,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>89</v>
@@ -26082,7 +26085,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>108</v>
@@ -26168,7 +26171,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>125</v>
@@ -26254,7 +26257,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>143</v>
@@ -26340,7 +26343,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26426,7 +26429,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>50</v>
@@ -26512,7 +26515,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26598,7 +26601,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>89</v>
@@ -26684,7 +26687,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>108</v>
@@ -26770,7 +26773,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>125</v>
@@ -26856,7 +26859,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>143</v>
@@ -26942,7 +26945,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -27028,7 +27031,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1446</v>
+        <v>1871</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>50</v>
@@ -27114,7 +27117,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1871</v>
+        <v>2306</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27200,7 +27203,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1871</v>
+        <v>2306</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>89</v>
@@ -27286,7 +27289,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1871</v>
+        <v>2306</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>108</v>
@@ -27372,7 +27375,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1871</v>
+        <v>2306</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>125</v>
@@ -27458,7 +27461,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1871</v>
+        <v>2306</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>143</v>
@@ -27544,7 +27547,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1871</v>
+        <v>2306</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27630,7 +27633,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1871</v>
+        <v>2306</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>50</v>
@@ -27716,7 +27719,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1871</v>
+        <v>2306</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27802,7 +27805,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1871</v>
+        <v>2306</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>89</v>
@@ -27888,7 +27891,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1871</v>
+        <v>2306</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>108</v>
@@ -27974,7 +27977,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1871</v>
+        <v>2306</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>125</v>
@@ -28060,7 +28063,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1871</v>
+        <v>2306</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>143</v>
@@ -28146,7 +28149,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1871</v>
+        <v>2306</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28232,7 +28235,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1871</v>
+        <v>2306</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>50</v>
@@ -28318,7 +28321,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1871</v>
+        <v>2306</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28404,7 +28407,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1871</v>
+        <v>5397</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>89</v>
@@ -28490,7 +28493,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1871</v>
+        <v>5397</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>108</v>
@@ -28576,7 +28579,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1871</v>
+        <v>5397</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>125</v>
@@ -28662,7 +28665,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1871</v>
+        <v>5397</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>143</v>
@@ -28748,7 +28751,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1871</v>
+        <v>5397</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28834,7 +28837,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1871</v>
+        <v>5397</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>50</v>
@@ -28920,7 +28923,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1871</v>
+        <v>5397</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -29006,7 +29009,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1871</v>
+        <v>5397</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>89</v>
@@ -29092,7 +29095,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1871</v>
+        <v>5397</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>108</v>
@@ -29178,7 +29181,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1871</v>
+        <v>5397</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>125</v>
@@ -29264,7 +29267,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1871</v>
+        <v>5397</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>143</v>
@@ -29350,7 +29353,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1871</v>
+        <v>5397</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29436,7 +29439,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1871</v>
+        <v>5397</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>50</v>
@@ -29522,7 +29525,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1871</v>
+        <v>5397</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29608,7 +29611,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1871</v>
+        <v>5397</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>89</v>
@@ -29694,7 +29697,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2306</v>
+        <v>5397</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>108</v>
@@ -29780,7 +29783,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2306</v>
+        <v>5397</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>125</v>
@@ -29866,7 +29869,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2306</v>
+        <v>5397</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>143</v>
@@ -29952,7 +29955,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2306</v>
+        <v>5397</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30038,7 +30041,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2306</v>
+        <v>5397</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>50</v>
@@ -30124,7 +30127,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2306</v>
+        <v>5397</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30210,7 +30213,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2306</v>
+        <v>5397</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>89</v>
@@ -30296,7 +30299,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2306</v>
+        <v>5397</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>108</v>
@@ -30382,7 +30385,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2306</v>
+        <v>5397</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>125</v>
@@ -30468,7 +30471,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2306</v>
+        <v>5397</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>143</v>
@@ -30554,7 +30557,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2306</v>
+        <v>5397</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30640,7 +30643,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2306</v>
+        <v>5397</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>50</v>
@@ -30726,7 +30729,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2306</v>
+        <v>5397</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30812,7 +30815,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2306</v>
+        <v>5397</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>89</v>
@@ -30898,7 +30901,7 @@
         <v>46188</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>2306</v>
+        <v>5397</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>108</v>
